--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O423"/>
+  <dimension ref="A1:O461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26967,6 +26967,2469 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:48:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>tell all the tokenmaxxers we’re comin https://t.co/boBI0pR9qR</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077797543224770940</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Ramp teased an upcoming launch or initiative aimed at the tokenmaxx community, indicating a forthcoming product or service rollout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:45:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>@karimatiyeh Enjoy, this one’s on us
+https://t.co/mz7ueJHHVt https://t.co/DDEsoKWZx4</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077796722911121449</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Ramp posted a friendly, promotional message offering something free to a user, indicating a marketing giveaway or product promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:39:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>@restocc @eglyman https://t.co/1UhZOsi225</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077795255747826093</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Ramp tagged Restocc and Eglyman in a post with a link, indicating a possible partnership or collaborative announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 15:04:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>@pontusab https://t.co/5qd1ddh4Gh</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077771237867086276</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>Ramp posted a link mentioning @pontusab, indicating a potential partnership or collaboration with Pontus AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 14:37:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>We analyzed 110 trillion tokens and found 3 distinct spending profiles with different model choices, caching habits, prompts, and spend controls.
+See how you compare.
+https://t.co/5sx7blcao1</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077764536048738685</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Ramp announced that it analyzed 110 trillion tokens, identifying three distinct spending profiles with varying model choices, caching habits, prompts, and spend controls, highlighting its data-driven insights into usage patterns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 14:35:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>No more trying to wrangle AI spend in the dark. 
+Connect your business data. Measure your team trends. Maximize value per token.
+There's a light up ahead. https://t.co/ocsftjOd4p</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077763942357619180</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>Ramp announced a new solution for managing AI spend, offering data integration, team trend measurement, and token value optimization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 14:21:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>@eglyman that's our CFO 💛 https://t.co/6eBcWiiPvI</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077760617516044682</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Leadership Changes</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Ramp publicly acknowledges its CFO, highlighting a leadership appointment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 20:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>BREX DATA: Three of the 25 most-purchased founder books this year are from @stripepress, with two more just outside the list. A payments company that launched a press in 2018 is quietly becoming the startup bookshelf.</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077845729960194441</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Brex highlights that its Stripe Press titles are among the top-purchased founder books, indicating growing influence of its publishing arm in the startup ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 19:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>BREX DATA: A year ago, Atomic Habits was the #3 book founders bought on Brex. Today it's #11, down 31%. Meanwhile, High Output Management is up 59%, and The Hard Thing About Hard Things and The Philosopher in the Valley are in the top 10.</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077830629526294858</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Brex shares updated data on the most popular books purchased by founders, highlighting shifts in rankings and growth for specific titles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 18:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>BREX DATA: Founder mode isn't just talk. It shows up in what founders buy. The most-purchased business book on Brex cards in H1 2026 is a brand-new biography of Alex Karp</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077815531114295744</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Brex highlights founder purchasing trends, noting the most-purchased business book on its cards in H1 2026 is a new biography of Alex Karp, reinforcing its founder-focused positioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:16:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>@WineDiarist @wguidara @martinkl @patricklencioni Read the rest: https://t.co/Gnre75JSbD</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077789599401681369</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Brex posted a link tagging multiple individuals, suggesting a collaborative or partnership announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:15:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>The Philosopher in the Valley by Michael Steinberger @WineDiarist
+Unreasonable Hospitality by Will Guidara @wguidara
+Designing Data-Intensive Applications by @martinkl
+The Five Dysfunctions of a Team
+by @patricklencioni
+The Challenger Sale by Dixon &amp; Adamson
+Traction by @GinoWickman
+Never Split the Difference by @fbinegotiator
+Radical Candor by @kimballscott
+The Hard Thing About Hard Things by @bhorowitz
+The Scaling Era by @dwarkesh_sp and @gleech
+Atomic Habits by @JamesClear
+Scaling People by @chughesjohnson
+High Output Management by Andy Grove
+Crucial Conversations by Patterson et al.
+The Mom Test by @robfitz
+Dare to Lead by @BreneBrown
+AI Engineering by @chipro
+What the Heck Is EOS? by @GinoWickman
+Extreme Ownership by @LeifBabin and @jockowillink
+The Creative Act by @RickRubin
+The Origins of Efficiency by @_brianpotter
+The Coaching Habit by @mbs_works
+The Goal by Eliyahu Goldratt
+No Rules Rules by @reedhastings and @ErinMeyerINSEAD
+Who by Smart &amp; Street</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077789133028684257</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>Brex shared a curated list of recommended books and resources, highlighting thought leadership and industry insights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:15:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Founder mode is back on the bookshelf.
+Book purchases across 35,000+ Brex customers. H1 2026's rankings show founder biographies reclaiming the top spot, @stripepress cementing itself as a startup staple, and management frameworks losing ground to AI. 
+See what's on the bookshelf in the comments.</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077789130646241494</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Brex highlights that over 35,000 customers are buying books, with founder biographies reclaiming the top spot, signaling a strategic focus on founder-oriented content and a shift toward AI-driven management insights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Heartshare</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>2026-07-16T17:47:57.180Z</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>We're still beaming from an unforgettable experience at the World Cup! ⚽✨
+Thanks to Airbnb’s incredible generosity, 50 young people from Heartshare's foster care programs had the chance to attend a FIFA World Cup 2026 match—a once-in-a-lifetime experience they'll never forget. We're deeply grateful to Airbnb for investing in young people and making this opportunity possible.
+A special thank you as well to New York City Council Member Rita Joseph for recommending Heartshare for this initiative and for being such a dedicated champion for our youth. Together, we're making dreams come true!</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5622AQHBua3f7o1sBA/feedshare-image-high-res/B56Z9ici6JG0AY-/0/1784063078272?e=1785974400&amp;v=beta&amp;t=pFuPI_TvjxJjRLxaEg7wOWJCABmvbM18dUvKXjEXfYg</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/heartshare_were-still-beaming-from-an-unforgettable-ugcPost-7482902912327761920-1Gwk</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>Airbnb funded a trip for 50 foster youth from Heartshare to attend a FIFA World Cup 2026 match, highlighting a community partnership supported by NYC Council Member Rita Joseph.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Planning a trip to Norway? 🇳🇴
+➡️ The Fjords: Glide through dark waters past towering cliffs and feel the cold mist from crashing waterfalls.
+➡️ The Light: Hike under the midnight sun and watch the sky turn brilliant shades of pink over rugged islands.
+➡️ The Stays: Skip standard hotels and warm up by the fire in a striking, repurposed red fisherman’s cabin right on the water
+🔗 Plan your travel: https://t.co/MZXIYNu96P</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2077906128151687668</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Expedia promotes travel to Norway, highlighting fjord cruises, midnight sun hikes, and unique cabin stays, and provides a link for users to plan their trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>2026-07-16T17:39:01.487Z</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Why is Croatia the ultimate summer destination? 🇭🇷
+➡️ Plitvice Lakes: Arrive early to walk the boardwalks past stunning waterfalls before the crowds.
+➡️ Island hopping: Swap busy Hvar for Vis to enjoy authentic fishing villages and hidden coves.
+➡️ Currency: Croatia now uses the Euro, making cross-border travel easier than ever.
+Find out more about Croatia here: http://ms.spr.ly/6040vIiNi</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D10AQFa0LscHeiFSA/image-shrink_1280/B4DZ9pJx08JAAg-/0/1784175599374?e=1784880000&amp;v=beta&amp;t=kMvzeFUVDhtRHxTUwvyQDnFZ1n6vEAyVCYg9d24Gq3I</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_why-is-croatia-the-ultimate-summer-destination-activity-7483575936953561088-kQBn</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>Expedia promotes Croatia as a top summer destination, emphasizing attractions like Plitvice Lakes, island hopping to Vis, and the convenience of the Euro, aiming to drive bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 07:44:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Hi Tom,
+You recently reached out to us in regards to your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please provide us with the following details :
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+Thank you.</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078022965799657485</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Booking.com posted a customer service message requesting reservation details to assist a user with a car rental inquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 07:43:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Hi Marisa 
+You recently reached out to us in regards to your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please provide us with the following details :
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+Thank you.</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078022846433902673</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Booking.com posted a customer service message following up on a user's car rental reservation request, asking for booking details to provide assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:46:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Hola, Paola. Sentimos que no hayas obtenido respuesta aún a tu solicitud. Cuéntanos, ¿cómo podemos ayudarte?. Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Además, por el momento solo ofrecemos soporte para reservas de alojamiento a través de las redes sociales. Para preguntas sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí:  https://t.co/TBejpc4vOA.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078008488534405244</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Booking.com posted a customer service message outlining how users can get support for accommodation reservations via private message, phone, or specialized teams for other services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:25:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Gracias por compartir tu situación. Por motivos de seguridad, no podemos ofrecer asistencia a nuestros colaboradores a través de las redes sociales. Sin embargo, puedes encontrar los datos de contacto de nuestro equipo de Ayuda para colaboradores aquí:  https://t.co/QpD1nP4Qdu?
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078003152226308395</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user query, stating they cannot provide assistance via social media for security reasons and directed the user to the collaborator help team's contact information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:23:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>@valarmorgulisse - Numéro de confirmation
+- Code confidentiel
+- Nom indiqué sur la réservation
+En alternative, pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078002648268042652</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user query with reservation confirmation details and provided a phone link for immediate assistance, indicating ongoing customer support activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:23:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>@valarmorgulisse Nous regrettons de lire votre déception. Afin que nous puissions vous aider ici, pourriez-vous nous envoyer un message privé avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078002563098579338</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user expressing disappointment, apologizing and requesting a private message with details to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:22:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>@valarmorgulisse Bonjour, toutes nos excuses pour le délai de réponse. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078002499441631324</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response, citing a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 01:31:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Hi Tawn, we regret to hear that your flight is delayed and we understand how important this is for you. As much as we would like to, we're unable to assist with Flight reservations through social media, but if you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077929105236918439</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user about a delayed flight, stating they cannot assist via social media and provided contact details for their Flights team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:53:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for sharing your concerns regarding the property at 40 Shaftesbury Avenue. We acknowledge your message and regret to hear about the issues that were summarized in recent reviews. It's important to know that we provide an online platform through which properties can advertise their service. By making a reservation, you enter into a direct (legally binding) contractual relationship with the accommodation provider and, from that point, we act solely as an intermediary between you and them.
+If you still need support, we'll be happy to check your case and assist you. Feel free to DM us the following details: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077919491325841739</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a customer complaint, clarifying its role as an intermediary and offering to assist with the reservation issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:27:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>@tdog1410 We have sent you a private message; kindly check at your earliest convenience. Thank you.</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077912949029568633</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user via private message, indicating a direct customer service interaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:22:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Hi Lios, thank you for flagging this. The properties provide the information on our website and have to pass a verification procedure before becoming bookable. If we find that a property listed on our platform is providing false information, we investigate immediately, give them the opportunity to rectify, or we may remove them from our website accordingly.
+Feel free to DM us with a link to the property's https://t.co/fGhmZE7riF page, as well as some more information about the details you believe are listed incorrectly, and our partner support team can investigate further.</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077911675949215879</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user flagging false property information, outlining its verification process and commitment to investigate and remove inaccurate listings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:06:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Hi Levi, we regret to hear about the challenges you're facing regarding your refund, and we want to help you resolve this issue. If you could please share more details about your concern, we would be more than happy to assist you in any way we can. If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077907733962010725</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user complaint about a refund, requesting booking details and directing the user to 24/7 support for faster assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 23:56:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Thank you for contacting us, Irfan, and we regret to hear about any inconvenience this has caused you regarding your booked reservation. However, it's important to know that we provide an online platform through which properties can advertise their services. By making a reservation, you enter into a direct (legally binding) contractual relationship with the accommodation provider and, from that point, we act solely as an intermediary between you and them.
+If you still need support, we’ll be happy to check your case and assist you. Feel free to DM us the following details:
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr"/>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077905261033861602</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a customer complaint, clarifying its role as an intermediary and offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 23:33:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about the difficulty you’ve experienced with your Prague booking. We understand how frustrating it must feel to cancel within minutes and still face a non‑refundable outcome, especially when you expected free cancellation. Please note that each accommodation provider manages their policies themselves, so whenever an out of policy cancellation is requested, only the accommodation provider can approve this as an exception, not https://t.co/fGhmZE7riF
+We'll be happy to reach out to the property on your behalf if you send us a private message with the following details:
+- Pin code:
+- Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077899490606879081</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a customer complaint, explaining that cancellation policies are managed by individual accommodation providers and offered to contact the property on the customer's behalf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 23:28:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Hi Shivam, we regret to hear about the distress this situation has caused you. It sounds like your booking didn't confirm successfully, but the payment was collected. Were you charged by https://t.co/fGhmZE7riF or by the accommodation? If we've charged you, our system will recognize that the payment isn't linked to a booking and automatically refund it back. Once the refund is processed, it can take 7-12 days to reflect in your account - you should've also received an email confirming this. 
+It's also possible that you made a typo when entering your email address, as you wouldn't receive the confirmation email afterward. If you send us a private message with the following details, we'll look into our system to see if we can locate your booking:
+• Name of the property: 
+• Dates of stay: 
+• Full guest name &amp; name of the person contacting us: 
+• Email address used to make the booking:</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077898128460591513</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user complaint about a failed booking confirmation and payment issue, outlining refund procedures and requesting details to investigate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 22:29:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>@anonemonk Hi there, thank you for contacting us. Kindly note that we have replied to your direct message, and please review it whenever you have the time. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077883317613924757</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Booking.com replied politely to a user inquiry on X, directing the user to a direct message for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 22:29:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out us. We regret that the property was unable to accommodate you. The availability of the rooms is set up by the properties themselves, and they're solely responsible for making sure this is correct. We don't decide on behalf of the property how many (if any) rooms they want to have available to book through our platform for any given date.
+If a property is unable to honor a booking, they should help you find another place to stay. If they're unable or unwilling to provide this, they should let us know as soon as possible so that we can help to find a solution. Please send us the following details via private message:
+• Confirmation number:
+• PIN code:
+• Name on the reservation:
+Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077883277638029662</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a customer complaint, clarifying that room availability is managed by properties and offering support channels for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 22:08:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>@sufyq Hi there, thank you for reaching out to us. We've sent you a private message. Kindly check it at your earliest convenience. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077878042563662126</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user inquiry, confirming a private message has been sent for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 21:30:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>@Chirag1060 We understand your frustration, Dinesh, and that you've already contacted our support team multiple times regarding your concern. However, due to GDPR laws, our specialized team is the only one with access to your information.</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr"/>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077868438576411123</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user complaint about support delays, citing GDPR restrictions on data access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 20:54:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Hi Ellie, we hope this message finds you well. We would like to take the opportunity to understand how we can assist you or provide support regarding your room and the overall experience you had during your previous stay with us. It is always our recommendation to communicate any concerns or issues directly to the accommodation provider while you are still on the premises, as it is in their best interest to ensure that your stay is as pleasant and comfortable as possible. 
+In order for us to provide you with the best assistance possible, we kindly ask you to send us a private message containing the following details:
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation: 
+We assure you that we will respond to your inquiry as soon as we can. Alternatively, if you require immediate assistance, you can always reach us by giving us a call at this number: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077859455333535894</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Booking.com posted a direct outreach message requesting personal reservation details via private message or phone, indicating a focus on post‑stay customer support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>2026-07-16T15:29:56.000Z</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>It’s so easy, even a teapot figured it out.</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>https://instagram.fosu2-1.fna.fbcdn.net/v/t51.71878-15/748745802_1323295810017600_7815082476634872487_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=instagram.fosu2-1.fna.fbcdn.net&amp;_nc_cat=100&amp;_nc_oc=Q6cZ2gFxZeZYC7uDiMS8MwgOYEbgOSh_YFgZQKvivX3ZOum4OR9pz4TlbtLxBCvp7hW6MWZ7E9mM_ilWsTB8syz--UV0&amp;_nc_ohc=8hc5mepczvsQ7kNvwFkjR6m&amp;_nc_gid=Eyhq7S_k6QSQG5oOFozTAQ&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQD6N0U0vkD5_SQYyeJHNPrNr6JB5FTmgOjdsPhRuaQvQQ&amp;oe=6A5FBA47&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>https://instagram.find1-1.fna.fbcdn.net/o1/v/t2/f2/m86/AQNoqvLWgA3FZJHwOwTkp1GsGxGzuqQnJzDBFwW8qvCWyJK82A4J6sl5T156wC59Td2_jpShNrnXqEjfVYtIM9ws_dAPRtXAIA-n6nA.mp4?_nc_cat=102&amp;_nc_oc=AdrjgU-Ivv5zjrKXVN1Qwv3EK8SbV-DkOvuDA5Ly4z9CcHKDP4ohmrew4zArgQKaRQk&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.find1-1.fna.fbcdn.net&amp;_nc_ohc=_Sa6BEPlaJUQ7kNvwG3i8iu&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MzA4NTY5ODkyNDk3MzIzMSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozMiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5030272038583226&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9BNzRDNEVDOEJFNzMyQkQ0MTdEOUM5QjJFRDNGQTk4RV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EyNEZGRjQwQzk5RTQ2OUE1NjhERDY0ODREQTc3QTlCX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbesvTEqJv7ChUCKAJDMywXQEARBiTdLxsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=jaCmhg0kyBrzR6wutyjvaA&amp;_nc_ss=72a8c&amp;_nc_zt=28&amp;oh=00_AQAhbe4UwCygRngSAln8kkWCo_gRSd6e4LoGzxwjdiw1dg&amp;oe=6A5BCA1B</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da29pUptA2J/</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Booking.com highlights the simplicity of a new feature or service, emphasizing that it's extremely easy to use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>2026-07-16T15:35:38.000Z</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>No humans. No drama. Just an Easy purr-cation.</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t51.71878-15/750376604_1749854193100334_7661202268487853117_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gEKJiR6enfHhE2lIlyBZadA_73rkKqzwccz1PWNOdB0oyxCuMtA5KKLU6jpjXGFyjS5t6N6hYTY247GXdw62X7y&amp;_nc_ohc=rSpQG2x4njUQ7kNvwG2SutW&amp;_nc_gid=r6kEqqjOwPgg-jeB2yeyNw&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQDfsNayEiem_apqHLscRPqcG9soncEH_3__kNyCpEowqw&amp;oe=6A5FAC5D&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>https://instagram.fagc3-2.fna.fbcdn.net/o1/v/t2/f2/m86/AQPgUW6PRwGNO-LWg9gTXbHYbEAdGZTdVygX-s5lkZY8xKYrF_oe61MFMa7AalMUjtamhOsKdLIyrOrTx-sqYCeujABRc26qDnBZlEI.mp4?_nc_cat=110&amp;_nc_oc=AdpXGNprx9zmxpeumXEl9cjbQfOE5pF2FilBj64xksKADBvGoex3lTdRD-q6t--oHXkbdzlVNQk11PHxoL_xBEQs&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.fagc3-2.fna.fbcdn.net&amp;_nc_ohc=sXs7N1pEz9AQ7kNvwHDzOf-&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTk2MTk2NzAwMTQyNTgzNSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozNiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=befb48259c2372c8&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9DRTQ1RUFCNUY4RTM0MTM2MEY4QkE0RkVBNjc2MzlBRl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlBNDVEMUQyREYzQzRFNDUwQTQ2MERBQTI2NTZBN0FDX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW3vKiwZn8BhUCKAJDMywXQEIVP3ztkWgYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=xGhbcZGm2vCw4iMssv8I3g&amp;_nc_ss=7ca8c&amp;_nc_map=urlgen_bucketless&amp;_nc_zt=28&amp;oh=00_AQCYClSlolRi3xGvrBP6TXfNvtOY_JAG2f6sY1jCRF2Bpg&amp;oe=6A5BB4F3</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da2-Un9tc84/</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Booking.com shared a lighthearted, pet‑focused post promoting an easy, hassle‑free travel experience for pets, indicating a marketing push for pet‑friendly bookings.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
